--- a/manufacturing_forms/010_material_specification_approval_request--manufacturing_forms.xlsx
+++ b/manufacturing_forms/010_material_specification_approval_request--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'material_type_1'}</t>
+          <t>material_type_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Material Type 1'}</t>
+          <t>Material Type 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'material_type_2'}</t>
+          <t>material_type_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Material Type 2'}</t>
+          <t>Material Type 2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'material_type_3'}</t>
+          <t>material_type_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Material Type 3'}</t>
+          <t>Material Type 3</t>
         </is>
       </c>
     </row>
